--- a/mapping/agg_rd_to_base/agg_rd_to_Patents_Citation.xlsx
+++ b/mapping/agg_rd_to_base/agg_rd_to_Patents_Citation.xlsx
@@ -500,12 +500,12 @@
     <row r="1" ht="20.15" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>nace_code</t>
+          <t>nace_code (RD)</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>aggregation</t>
+          <t>nace_code (aggregated)</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
     <row r="1" ht="20.15" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>country_code</t>
+          <t>country_code (RD)</t>
         </is>
       </c>
       <c r="B1" s="7" t="inlineStr">
         <is>
-          <t>aggregation</t>
+          <t>country_code (aggregated)</t>
         </is>
       </c>
     </row>
